--- a/data/trans_dic/P32-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensa que debería beber menos</t>
+          <t>Población que piensa que debería beber menos (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,81</t>
+          <t>0,32; 3,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,15</t>
+          <t>3,16; 9,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,71</t>
+          <t>3,56; 10,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,05</t>
+          <t>3,18; 9,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,95</t>
+          <t>0,79; 9,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 10,24</t>
+          <t>1,81; 9,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,98</t>
+          <t>1,25; 6,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,07</t>
+          <t>0,46; 3,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,53</t>
+          <t>2,89; 7,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,08</t>
+          <t>3,58; 8,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,38</t>
+          <t>3,12; 7,06</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,56</t>
+          <t>0,48; 4,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 10,05</t>
+          <t>3,02; 10,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 8,07</t>
+          <t>2,46; 7,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,96</t>
+          <t>1,6; 6,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,94</t>
+          <t>0,81; 8,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 7,62</t>
+          <t>1,65; 8,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,39</t>
+          <t>1,56; 7,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,19</t>
+          <t>0,55; 3,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,21</t>
+          <t>2,89; 7,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,64</t>
+          <t>2,67; 6,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,79</t>
+          <t>2,06; 5,94</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,99</t>
+          <t>1,65; 5,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 8,73</t>
+          <t>3,54; 8,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,93</t>
+          <t>1,94; 6,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 10,48</t>
+          <t>3,6; 10,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 10,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,49</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 14,28</t>
+          <t>1,77; 15,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,02</t>
+          <t>0,0; 9,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,27</t>
+          <t>1,73; 5,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,9</t>
+          <t>3,32; 7,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,48</t>
+          <t>2,18; 6,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,14</t>
+          <t>3,4; 9,44</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,07</t>
+          <t>1,91; 4,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,68</t>
+          <t>5,48; 9,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,26</t>
+          <t>3,61; 7,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,07</t>
+          <t>3,74; 9,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,22</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,53</t>
+          <t>0,42; 3,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,76</t>
+          <t>0,99; 4,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,69</t>
+          <t>0,04; 2,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,07</t>
+          <t>1,71; 3,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,56</t>
+          <t>4,33; 7,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,92</t>
+          <t>3,12; 5,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,86</t>
+          <t>1,69; 5,76</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 6,04</t>
+          <t>0,84; 6,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,95</t>
+          <t>2,87; 7,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,75</t>
+          <t>3,11; 8,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 12,28</t>
+          <t>4,98; 12,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 9,3</t>
+          <t>1,42; 9,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,39</t>
+          <t>0,57; 5,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,76</t>
+          <t>1,58; 7,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,79</t>
+          <t>1,59; 5,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,08</t>
+          <t>2,37; 5,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,96</t>
+          <t>2,3; 5,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 9,2</t>
+          <t>4,3; 9,32</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 8,97</t>
+          <t>1,84; 7,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,21; 20,96</t>
+          <t>8,82; 21,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,65; 14,6</t>
+          <t>4,52; 14,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 27,39</t>
+          <t>1,88; 26,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,37 +1442,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,45</t>
+          <t>0,37; 3,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,64</t>
+          <t>2,14; 7,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,74</t>
+          <t>0,79; 3,61</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,74</t>
+          <t>3,75; 8,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,11</t>
+          <t>3,85; 8,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 12,31</t>
+          <t>1,61; 13,21</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,58</t>
+          <t>2,1; 3,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,01</t>
+          <t>5,58; 7,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 6,4</t>
+          <t>4,24; 6,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,69</t>
+          <t>5,02; 7,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,54</t>
+          <t>0,79; 2,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,38</t>
+          <t>1,36; 3,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,57</t>
+          <t>2,28; 4,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,34</t>
+          <t>0,97; 3,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,94</t>
+          <t>1,81; 2,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,08</t>
+          <t>4,38; 6,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,33</t>
+          <t>3,83; 5,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,72</t>
+          <t>3,38; 5,68</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensa que debería beber menos</t>
+          <t>Población que piensa que debería beber menos (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>979; 11038</t>
+          <t>942; 11020</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9204; 26864</t>
+          <t>9262; 27507</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10437; 28049</t>
+          <t>10277; 28979</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9609; 25569</t>
+          <t>8976; 25550</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5278</t>
+          <t>0; 5961</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1199; 13345</t>
+          <t>1183; 13918</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2914; 15769</t>
+          <t>2782; 14292</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1919; 11366</t>
+          <t>2039; 11240</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2506; 12822</t>
+          <t>1911; 12705</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12610; 33308</t>
+          <t>12805; 34631</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15604; 35777</t>
+          <t>15856; 36599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13528; 32878</t>
+          <t>13909; 31437</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1087; 10171</t>
+          <t>1061; 10236</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7223; 25468</t>
+          <t>7649; 25472</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6095; 19298</t>
+          <t>5877; 18746</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3523; 14833</t>
+          <t>3399; 14669</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7162</t>
+          <t>0; 6914</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1135; 12738</t>
+          <t>1159; 12245</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3154; 14511</t>
+          <t>3151; 15538</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2221; 9851</t>
+          <t>2083; 10037</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2153; 12044</t>
+          <t>2080; 12005</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11156; 32516</t>
+          <t>11436; 31285</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11606; 28508</t>
+          <t>11481; 28758</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7270; 20046</t>
+          <t>7139; 20579</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5904; 20284</t>
+          <t>5579; 18937</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13599; 33907</t>
+          <t>13725; 32586</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5682; 19752</t>
+          <t>6449; 20576</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8281; 22143</t>
+          <t>7608; 22510</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5729</t>
+          <t>0; 6256</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5960</t>
+          <t>0; 6378</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>955; 8071</t>
+          <t>1001; 8568</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4042</t>
+          <t>0; 3801</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6649; 21096</t>
+          <t>6944; 21622</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15755; 36943</t>
+          <t>15507; 36214</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8631; 25253</t>
+          <t>8506; 24279</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8556; 22990</t>
+          <t>8543; 23754</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13453; 33957</t>
+          <t>12786; 31918</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36608; 63956</t>
+          <t>36192; 65902</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23243; 47699</t>
+          <t>23705; 47738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19405; 46223</t>
+          <t>19086; 46235</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 8164</t>
+          <t>0; 8566</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>969; 8151</t>
+          <t>979; 8302</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3093; 14129</t>
+          <t>2932; 13447</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>253; 11138</t>
+          <t>164; 11291</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14381; 35146</t>
+          <t>14774; 34209</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39535; 67476</t>
+          <t>38650; 67717</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29088; 56442</t>
+          <t>29778; 55533</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15794; 54178</t>
+          <t>15599; 53232</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1874; 13050</t>
+          <t>1823; 13734</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9040; 24191</t>
+          <t>8736; 23456</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10073; 27595</t>
+          <t>9802; 28333</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11463; 28467</t>
+          <t>11546; 29570</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1988; 13053</t>
+          <t>1987; 12785</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1078; 9918</t>
+          <t>1040; 10354</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6385</t>
+          <t>0; 6784</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2211; 8861</t>
+          <t>2073; 9273</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5060; 20630</t>
+          <t>5676; 20609</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11448; 29687</t>
+          <t>11570; 28772</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11233; 30101</t>
+          <t>11603; 29634</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15647; 33409</t>
+          <t>15624; 33816</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2533; 12520</t>
+          <t>2565; 11139</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12860; 29263</t>
+          <t>12314; 30446</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7477; 23498</t>
+          <t>7276; 22555</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1753; 25985</t>
+          <t>1780; 24950</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4723</t>
+          <t>0; 4713</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>984; 9075</t>
+          <t>961; 9595</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5716; 19545</t>
+          <t>5464; 19093</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 11422</t>
+          <t>0; 11404</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2815; 13347</t>
+          <t>2804; 12891</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16118; 35212</t>
+          <t>15100; 33835</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16483; 37978</t>
+          <t>16034; 36796</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2396; 26613</t>
+          <t>3481; 28558</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>38112; 67172</t>
+          <t>39490; 67595</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>115388; 163330</t>
+          <t>113789; 162917</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87095; 127649</t>
+          <t>84611; 128871</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76033; 118659</t>
+          <t>77471; 121544</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6959; 22689</t>
+          <t>7108; 22856</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14149; 35439</t>
+          <t>14267; 34492</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26548; 52214</t>
+          <t>26063; 50746</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10005; 33533</t>
+          <t>9688; 32428</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>48257; 81390</t>
+          <t>50143; 82514</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>136050; 187917</t>
+          <t>135166; 187661</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>118184; 167296</t>
+          <t>120108; 169546</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>89023; 145730</t>
+          <t>86052; 144712</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,8</t>
+          <t>0,33; 4,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 9,37</t>
+          <t>3,46; 9,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 10,04</t>
+          <t>3,4; 9,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,04</t>
+          <t>3,58; 9,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 9,33</t>
+          <t>0,8; 8,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,28</t>
+          <t>1,6; 9,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,91</t>
+          <t>1,52; 7,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,04</t>
+          <t>0,46; 3,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,82</t>
+          <t>2,85; 7,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,27</t>
+          <t>3,5; 8,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,06</t>
+          <t>3,35; 7,38</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,59</t>
+          <t>0,48; 4,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 10,05</t>
+          <t>2,93; 10,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 7,84</t>
+          <t>2,43; 8,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,89</t>
+          <t>2,02; 7,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,59</t>
+          <t>1,25; 8,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 8,15</t>
+          <t>1,67; 7,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,53</t>
+          <t>1,96; 8,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,18</t>
+          <t>0,53; 3,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,9</t>
+          <t>2,89; 8,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,69</t>
+          <t>2,6; 6,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,94</t>
+          <t>2,38; 6,43</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,59</t>
+          <t>1,88; 5,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,39</t>
+          <t>3,42; 8,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,17</t>
+          <t>1,9; 6,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 10,65</t>
+          <t>4,01; 11,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 9,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 15,16</t>
+          <t>1,78; 16,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,42</t>
+          <t>0,0; 8,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,4</t>
+          <t>1,64; 5,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,74</t>
+          <t>3,44; 8,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,23</t>
+          <t>2,15; 6,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,44</t>
+          <t>3,63; 9,71</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,77</t>
+          <t>1,9; 4,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,97</t>
+          <t>5,7; 9,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,27</t>
+          <t>3,44; 7,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 9,07</t>
+          <t>3,93; 8,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,59</t>
+          <t>0,42; 3,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,53</t>
+          <t>1,02; 4,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,73</t>
+          <t>0,77; 6,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,96</t>
+          <t>1,66; 3,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,59</t>
+          <t>4,44; 7,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,82</t>
+          <t>2,96; 5,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,76</t>
+          <t>3,3; 7,07</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 6,36</t>
+          <t>0,91; 6,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,71</t>
+          <t>2,96; 8,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,98</t>
+          <t>3,21; 8,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 12,75</t>
+          <t>5,53; 13,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 9,11</t>
+          <t>1,41; 8,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,62</t>
+          <t>0,58; 5,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,07</t>
+          <t>1,6; 6,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,78</t>
+          <t>1,76; 5,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,89</t>
+          <t>2,52; 6,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,86</t>
+          <t>2,25; 6,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,32</t>
+          <t>4,7; 9,65</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,98</t>
+          <t>1,43; 8,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,82; 21,81</t>
+          <t>9,3; 21,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,52; 14,02</t>
+          <t>4,61; 14,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 26,3</t>
+          <t>1,82; 22,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,64</t>
+          <t>0,38; 3,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,46</t>
+          <t>2,2; 7,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,61</t>
+          <t>0,78; 3,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,4</t>
+          <t>3,73; 8,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,83</t>
+          <t>3,8; 8,57</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 13,21</t>
+          <t>1,08; 10,73</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,6</t>
+          <t>2,03; 3,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,58; 7,99</t>
+          <t>5,63; 8,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,46</t>
+          <t>4,27; 6,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 7,88</t>
+          <t>5,32; 8,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,55</t>
+          <t>0,8; 2,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,29</t>
+          <t>1,33; 3,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,44</t>
+          <t>2,32; 4,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,23</t>
+          <t>2,0; 4,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,98</t>
+          <t>1,81; 2,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,07</t>
+          <t>4,45; 6,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,4</t>
+          <t>3,78; 5,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,68</t>
+          <t>4,37; 6,34</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21338</t>
+          <t>24796</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>942; 11020</t>
+          <t>969; 12169</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9262; 27507</t>
+          <t>10157; 27619</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10277; 28979</t>
+          <t>9833; 27077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8976; 25550</t>
+          <t>10871; 28555</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5961</t>
+          <t>0; 5116</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1183; 13918</t>
+          <t>1195; 12836</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2782; 14292</t>
+          <t>2456; 14152</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2039; 11240</t>
+          <t>2669; 13316</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1911; 12705</t>
+          <t>1917; 12739</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12805; 34631</t>
+          <t>12627; 34169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15856; 36599</t>
+          <t>15493; 36831</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13909; 31437</t>
+          <t>16036; 35359</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>15324</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1061; 10236</t>
+          <t>1067; 10460</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7649; 25472</t>
+          <t>7413; 26423</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5877; 18746</t>
+          <t>5815; 19583</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3399; 14669</t>
+          <t>4535; 16929</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6914</t>
+          <t>0; 6392</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1159; 12245</t>
+          <t>1787; 12064</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3151; 15538</t>
+          <t>3185; 14770</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2083; 10037</t>
+          <t>2844; 12139</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2080; 12005</t>
+          <t>2014; 12105</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11436; 31285</t>
+          <t>11430; 32757</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11481; 28758</t>
+          <t>11157; 27493</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7139; 20579</t>
+          <t>8812; 23787</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>806</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>16640</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5579; 18937</t>
+          <t>6369; 19938</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13725; 32586</t>
+          <t>13291; 33615</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6449; 20576</t>
+          <t>6326; 21192</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7608; 22510</t>
+          <t>9148; 26242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6256</t>
+          <t>0; 6165</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6378</t>
+          <t>0; 5890</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1001; 8568</t>
+          <t>1006; 9337</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3801</t>
+          <t>0; 4169</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6944; 21622</t>
+          <t>6573; 22172</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15507; 36214</t>
+          <t>16090; 38348</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8506; 24279</t>
+          <t>8373; 25677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8543; 23754</t>
+          <t>9962; 26684</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30506</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>37666</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12786; 31918</t>
+          <t>12692; 31468</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36192; 65902</t>
+          <t>37698; 65026</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23705; 47738</t>
+          <t>22606; 47999</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19086; 46235</t>
+          <t>21346; 47642</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 8566</t>
+          <t>0; 8750</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>979; 8302</t>
+          <t>970; 7938</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2932; 13447</t>
+          <t>3013; 13311</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>164; 11291</t>
+          <t>1766; 14354</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14774; 34209</t>
+          <t>14354; 33543</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38650; 67717</t>
+          <t>39604; 71147</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29778; 55533</t>
+          <t>28174; 54960</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15599; 53232</t>
+          <t>25515; 54599</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23560</t>
+          <t>28258</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1823; 13734</t>
+          <t>1972; 13432</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8736; 23456</t>
+          <t>9006; 25109</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9802; 28333</t>
+          <t>10133; 27891</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11546; 29570</t>
+          <t>14254; 34596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1987; 12785</t>
+          <t>1985; 12334</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1040; 10354</t>
+          <t>1073; 9994</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6784</t>
+          <t>0; 7072</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2073; 9273</t>
+          <t>2451; 10221</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5676; 20609</t>
+          <t>6279; 21225</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11570; 28772</t>
+          <t>12327; 29725</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11603; 29634</t>
+          <t>11355; 30511</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15624; 33816</t>
+          <t>19326; 39652</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>10166</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2565; 11139</t>
+          <t>1988; 12075</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12314; 30446</t>
+          <t>12981; 30676</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7276; 22555</t>
+          <t>7423; 23190</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1780; 24950</t>
+          <t>1558; 19666</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4713</t>
+          <t>0; 4694</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>961; 9595</t>
+          <t>1007; 9679</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5464; 19093</t>
+          <t>5625; 19398</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 11404</t>
+          <t>0; 11629</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2804; 12891</t>
+          <t>2775; 12327</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15100; 33835</t>
+          <t>15021; 34485</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16034; 36796</t>
+          <t>15829; 35732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3481; 28558</t>
+          <t>2296; 22791</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95917</t>
+          <t>106612</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>26238</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>117059</t>
+          <t>132850</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>39490; 67595</t>
+          <t>38195; 67278</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>113789; 162917</t>
+          <t>114853; 164126</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>84611; 128871</t>
+          <t>85209; 127459</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77471; 121544</t>
+          <t>87446; 132089</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7108; 22856</t>
+          <t>7166; 22250</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14267; 34492</t>
+          <t>13923; 35004</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26063; 50746</t>
+          <t>26561; 50924</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9688; 32428</t>
+          <t>17572; 37546</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50143; 82514</t>
+          <t>50300; 82002</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>135166; 187661</t>
+          <t>137634; 187683</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>120108; 169546</t>
+          <t>118652; 167685</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>86052; 144712</t>
+          <t>110110; 159679</t>
         </is>
       </c>
     </row>
